--- a/ig/DM-MAI-2026/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
+++ b/ig/DM-MAI-2026/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260505120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1207,13 +1207,13 @@
     <t>157</t>
   </si>
   <si>
-    <t>Urgences polyvalentes</t>
+    <t>Urgences polyvalentes hospitalières</t>
   </si>
   <si>
     <t>158</t>
   </si>
   <si>
-    <t>Urgences psychiatriques</t>
+    <t>Urgences psychiatriques hospitalières</t>
   </si>
   <si>
     <t>159</t>
@@ -1525,7 +1525,7 @@
     <t>201</t>
   </si>
   <si>
-    <t>Pédicure-Podologie</t>
+    <t>Pédicurie-Podologie (bilan diagnostic et mise en œuvre des activités thérapeutiques si nécessaire)</t>
   </si>
   <si>
     <t>Discipline paramédicale qualifiée pour traiter directement les affections épidermiques, limitées aux couches cornées et aux affections unguéales du pied, à l'exclusion de toute intervention chirurgicale, pour pratiquer les soins d'hygiène, pour confectionner et appliquer des semelles destinées à prévenir ou à soulager les affections épidermiques, pour analyser et évaluer les troubles morphostatiques et dynamiques du pied et élaborer un diagnostic de pédicurie-podologie en tenant compte de la statique et de la dynamique du pied, pour renouveler les prescriptions médicales initiales d'orthèses plantaires.</t>
@@ -1846,7 +1846,7 @@
     <t>249</t>
   </si>
   <si>
-    <t>Urgences pédiatriques</t>
+    <t>Urgences pédiatriques hospitalières</t>
   </si>
   <si>
     <t>250</t>
